--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C724CB-779D-A94F-AD62-C61A67032B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D92122E-FE57-9F49-983E-C1D4E20BD6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="136">
   <si>
     <t>Pin</t>
   </si>
@@ -380,12 +380,6 @@
     <t>SYNC Button</t>
   </si>
   <si>
-    <t>BEACON JMP</t>
-  </si>
-  <si>
-    <t>ATU Enable pulse</t>
-  </si>
-  <si>
     <t>JS8LED</t>
   </si>
   <si>
@@ -404,9 +398,6 @@
     <t>RF Signal Out (TX)</t>
   </si>
   <si>
-    <t>Beacon select Jumper</t>
-  </si>
-  <si>
     <t>RXA</t>
   </si>
   <si>
@@ -447,6 +438,12 @@
   </si>
   <si>
     <t>Driver Enable</t>
+  </si>
+  <si>
+    <t>BEACON SW</t>
+  </si>
+  <si>
+    <t>Beacon Jumper</t>
   </si>
 </sst>
 </file>
@@ -749,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -862,16 +859,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -880,7 +867,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1202,53 +1189,53 @@
         <v>107</v>
       </c>
       <c r="J3" s="60" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K3" s="60" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="70">
+      <c r="B4" s="22">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72" t="s">
+      <c r="D4" s="24"/>
+      <c r="E4" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="38"/>
       <c r="J4" s="61"/>
       <c r="K4" s="61"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="64">
+      <c r="B5" s="22">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="68"/>
+      <c r="H5" s="38"/>
       <c r="J5" s="61"/>
       <c r="K5" s="61"/>
     </row>
@@ -1322,7 +1309,7 @@
         <v>96</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K8" s="61"/>
     </row>
@@ -1350,7 +1337,7 @@
         <v>97</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K9" s="61"/>
     </row>
@@ -1418,13 +1405,13 @@
         <v>69</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H12" s="31" t="s">
         <v>109</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K12" s="61"/>
     </row>
@@ -1446,13 +1433,13 @@
         <v>69</v>
       </c>
       <c r="G13" s="45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H13" s="45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K13" s="61"/>
     </row>
@@ -1474,13 +1461,13 @@
         <v>88</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J14" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K14" s="61"/>
     </row>
@@ -1500,13 +1487,13 @@
         <v>89</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K15" s="61"/>
     </row>
@@ -1550,7 +1537,7 @@
         <v>110</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K17" s="61"/>
     </row>
@@ -1576,7 +1563,7 @@
         <v>111</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K18" s="61"/>
     </row>
@@ -1598,10 +1585,10 @@
         <v>78</v>
       </c>
       <c r="G19" s="46" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="J19" s="61"/>
       <c r="K19" s="61"/>
@@ -1624,10 +1611,10 @@
         <v>79</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="J20" s="61"/>
       <c r="K20" s="61"/>
@@ -1669,35 +1656,32 @@
         <v>108</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J22" s="61"/>
       <c r="K22" s="61"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="12">
+      <c r="B23" s="64">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14" t="s">
+      <c r="D23" s="66"/>
+      <c r="E23" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>59</v>
-      </c>
+      <c r="G23" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="38"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="61"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
@@ -1723,7 +1707,7 @@
         <v>47</v>
       </c>
       <c r="K24" s="63" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
@@ -1749,7 +1733,7 @@
         <v>48</v>
       </c>
       <c r="K25" s="63" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
@@ -1771,27 +1755,27 @@
       <c r="K26" s="61"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="70">
+      <c r="B27" s="22">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C27" s="71" t="s">
+      <c r="C27" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72" t="s">
+      <c r="D27" s="24"/>
+      <c r="E27" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="74" t="s">
+      <c r="G27" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="H27" s="74"/>
+      <c r="H27" s="38"/>
       <c r="J27" s="61"/>
       <c r="K27" s="63" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
@@ -1940,39 +1924,38 @@
         <v>71</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J34" s="61"/>
       <c r="K34" s="63" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="64">
+      <c r="B35" s="22">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66" t="s">
+      <c r="D35" s="24"/>
+      <c r="E35" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="67" t="s">
+      <c r="F35" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="G35" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="H35" s="68"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="65"/>
+      <c r="H35" s="38"/>
+      <c r="J35" s="23"/>
       <c r="K35" s="63" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
@@ -2051,7 +2034,7 @@
       </c>
       <c r="H39" s="37"/>
       <c r="J39" s="62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K39" s="61"/>
     </row>

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D92122E-FE57-9F49-983E-C1D4E20BD6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60C8EA-F834-924C-8B80-C5DAC100372E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
   <si>
     <t>Pin</t>
   </si>
@@ -440,10 +440,16 @@
     <t>Driver Enable</t>
   </si>
   <si>
-    <t>BEACON SW</t>
-  </si>
-  <si>
-    <t>Beacon Jumper</t>
+    <t>RFLO</t>
+  </si>
+  <si>
+    <t>RX Local Oscillator</t>
+  </si>
+  <si>
+    <t>RFIF</t>
+  </si>
+  <si>
+    <t>RF RX IF (465 KHz)</t>
   </si>
 </sst>
 </file>
@@ -746,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -859,15 +865,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1594,26 +1592,26 @@
       <c r="K19" s="61"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="40">
+      <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="34" t="s">
         <v>135</v>
       </c>
       <c r="J20" s="61"/>
@@ -1662,25 +1660,26 @@
       <c r="K22" s="61"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="64">
+      <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="68"/>
+      <c r="G23" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>137</v>
+      </c>
       <c r="J23" s="61"/>
       <c r="K23" s="61"/>
     </row>

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60C8EA-F834-924C-8B80-C5DAC100372E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD8DFD-D9A1-D241-8F23-1903CF70BD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
   <si>
     <t>Pin</t>
   </si>
@@ -450,6 +450,18 @@
   </si>
   <si>
     <t>RF RX IF (465 KHz)</t>
+  </si>
+  <si>
+    <t>SDA(1)</t>
+  </si>
+  <si>
+    <t>SCL(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2C SDA </t>
+  </si>
+  <si>
+    <t>I2C SCL</t>
   </si>
 </sst>
 </file>
@@ -752,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -789,14 +801,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -866,6 +873,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1180,62 +1195,62 @@
       <c r="F3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="60" t="s">
+      <c r="J3" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="K3" s="57" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="22">
+      <c r="B4" s="19">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="21"/>
+      <c r="E4" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
+      <c r="H4" s="35"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="22">
+      <c r="B5" s="19">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
+      <c r="H5" s="35"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="8">
@@ -1248,12 +1263,12 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
       <c r="J6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="61"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="12">
@@ -1272,16 +1287,16 @@
       <c r="F7" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="28" t="s">
         <v>95</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="61"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="12">
@@ -1300,16 +1315,16 @@
       <c r="F8" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="28" t="s">
         <v>96</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="K8" s="61"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="12">
@@ -1328,16 +1343,16 @@
       <c r="F9" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="28" t="s">
         <v>97</v>
       </c>
       <c r="J9" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="61"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="12">
@@ -1356,16 +1371,16 @@
       <c r="F10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="28" t="s">
         <v>98</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="61"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
@@ -1378,12 +1393,12 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
       <c r="J11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="61"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="12">
@@ -1402,16 +1417,16 @@
       <c r="F12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="J12" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="61"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="12">
@@ -1430,23 +1445,23 @@
       <c r="F13" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="42" t="s">
         <v>118</v>
       </c>
       <c r="J13" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="61"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="40">
+      <c r="B14" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="38" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="14" t="s">
@@ -1458,16 +1473,16 @@
       <c r="F14" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="41" t="s">
+      <c r="J14" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="K14" s="61"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="12">
@@ -1484,16 +1499,16 @@
       <c r="F15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="28" t="s">
         <v>133</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="K15" s="61"/>
+      <c r="K15" s="58"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
@@ -1506,19 +1521,19 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
       <c r="J16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="61"/>
+      <c r="K16" s="58"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="40">
+      <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="38" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="6"/>
@@ -1528,23 +1543,23 @@
       <c r="F17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="61"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="40">
+      <c r="B18" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="38" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="6"/>
@@ -1554,42 +1569,42 @@
       <c r="F18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="41" t="s">
+      <c r="J18" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="K18" s="61"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="40">
+      <c r="B19" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
@@ -1608,14 +1623,14 @@
       <c r="F20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
@@ -1628,12 +1643,12 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
       <c r="J21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="61"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
@@ -1650,14 +1665,14 @@
       <c r="F22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="4">
@@ -1674,64 +1689,64 @@
       <c r="F23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="22">
+      <c r="B24" s="19">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35" t="s">
+      <c r="D24" s="32"/>
+      <c r="E24" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="H24" s="38"/>
-      <c r="J24" s="61" t="s">
+      <c r="H24" s="35"/>
+      <c r="J24" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="63" t="s">
+      <c r="K24" s="60" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="22">
+      <c r="B25" s="19">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35" t="s">
+      <c r="D25" s="32"/>
+      <c r="E25" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="H25" s="38"/>
-      <c r="J25" s="61" t="s">
+      <c r="H25" s="35"/>
+      <c r="J25" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="63" t="s">
+      <c r="K25" s="60" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1746,108 +1761,108 @@
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
       <c r="J26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K26" s="61"/>
+      <c r="K26" s="58"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="22">
+      <c r="B27" s="19">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24" t="s">
+      <c r="D27" s="21"/>
+      <c r="E27" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="H27" s="38"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="63" t="s">
+      <c r="H27" s="35"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="60" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="22">
+      <c r="B28" s="19">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="38"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
+      <c r="H28" s="35"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="22">
+      <c r="B29" s="19">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="38" t="s">
+      <c r="G29" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="38"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
+      <c r="H29" s="35"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="22">
+      <c r="B30" s="19">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="H30" s="38"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
+      <c r="H30" s="35"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
@@ -1860,200 +1875,204 @@
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
       <c r="J31" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K31" s="61"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="22">
+      <c r="B32" s="19">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24" t="s">
+      <c r="D32" s="21"/>
+      <c r="E32" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F32" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="G32" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="H32" s="38"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
+      <c r="H32" s="35"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="22">
+      <c r="B33" s="19">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="38" t="s">
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="H33" s="38"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
+      <c r="H33" s="35"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="18">
+      <c r="B34" s="62">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20" t="s">
+      <c r="D34" s="64"/>
+      <c r="E34" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="44" t="s">
+      <c r="G34" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="H34" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="J34" s="58"/>
+      <c r="K34" s="60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="62">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="20"/>
+      <c r="K35" s="60" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="23">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="J36" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="58"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="19">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H37" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="J34" s="61"/>
-      <c r="K34" s="63" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="22">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="38"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="63" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="26">
-        <f t="shared" si="0"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B38" s="19">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="H36" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="J36" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="K36" s="61"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B37" s="22">
-        <f t="shared" si="0"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B39" s="19">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="38"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B38" s="22">
-        <f t="shared" si="0"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39" s="34"/>
+      <c r="J39" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="K39" s="58"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B40" s="19">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B39" s="22">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H39" s="37"/>
-      <c r="J39" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="K39" s="61"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B40" s="22">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="37" t="s">
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="H40" s="37"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
+      <c r="H40" s="34"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
@@ -2066,48 +2085,48 @@
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
       <c r="J41" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K41" s="61"/>
+      <c r="K41" s="58"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B42" s="47">
+      <c r="B42" s="44">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C42" s="48" t="s">
+      <c r="C42" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="57" t="s">
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="51"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
+      <c r="H42" s="48"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="58"/>
     </row>
     <row r="43" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="52">
+      <c r="B43" s="49">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C43" s="53" t="s">
+      <c r="C43" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="58" t="s">
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H43" s="56"/>
-      <c r="J43" s="61"/>
-      <c r="K43" s="61"/>
+      <c r="H43" s="53"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2125,7 +2144,7 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="56">
         <f>E2*6.25</f>
         <v>0</v>
       </c>
@@ -2135,7 +2154,7 @@
         <f>E2+1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="59">
+      <c r="F3" s="56">
         <f t="shared" ref="F3:F9" si="0">E3*6.25</f>
         <v>6.25</v>
       </c>
@@ -2145,7 +2164,7 @@
         <f t="shared" ref="E4:E9" si="1">E3+1</f>
         <v>2</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="56">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
@@ -2155,7 +2174,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="56">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
@@ -2165,7 +2184,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="56">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -2175,7 +2194,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="56">
         <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
@@ -2185,7 +2204,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="56">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
@@ -2195,7 +2214,7 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="56">
         <f t="shared" si="0"/>
         <v>43.75</v>
       </c>

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD8DFD-D9A1-D241-8F23-1903CF70BD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A808A401-4DEF-F24E-8B7E-1318F4C4FC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="144">
   <si>
     <t>Pin</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t>I2C SCL</t>
+  </si>
+  <si>
+    <t>rp2040Z</t>
+  </si>
+  <si>
+    <t>Not used</t>
   </si>
 </sst>
 </file>
@@ -503,7 +509,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -564,6 +570,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -764,7 +776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -881,6 +893,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,7 +1178,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K43"/>
+  <dimension ref="B2:L43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
@@ -1175,11 +1189,11 @@
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,14 +1215,17 @@
       <c r="H3" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="L3" s="57" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="19">
         <f>1</f>
         <v>1</v>
@@ -1227,10 +1244,13 @@
         <v>106</v>
       </c>
       <c r="H4" s="35"/>
-      <c r="J4" s="58"/>
+      <c r="J4" s="66" t="s">
+        <v>143</v>
+      </c>
       <c r="K4" s="58"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L4" s="58"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="19">
         <f>B4+1</f>
         <v>2</v>
@@ -1249,10 +1269,13 @@
         <v>106</v>
       </c>
       <c r="H5" s="35"/>
-      <c r="J5" s="58"/>
+      <c r="J5" s="66" t="s">
+        <v>143</v>
+      </c>
       <c r="K5" s="58"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L5" s="58"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="8">
         <f t="shared" ref="B6:B43" si="0">B5+1</f>
         <v>3</v>
@@ -1265,12 +1288,13 @@
       <c r="F6" s="11"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="36"/>
+      <c r="K6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="58"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L6" s="58"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="12">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1293,12 +1317,15 @@
       <c r="H7" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="58"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="58"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1321,12 +1348,15 @@
       <c r="H8" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="K8" s="58"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="58"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1349,12 +1379,15 @@
       <c r="H9" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="58"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="58"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="12">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1377,12 +1410,15 @@
       <c r="H10" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="58"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="58"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1395,12 +1431,13 @@
       <c r="F11" s="11"/>
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="36"/>
+      <c r="K11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="58"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="58"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="12">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1423,12 +1460,15 @@
       <c r="H12" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="58"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="L12" s="58"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1451,12 +1491,15 @@
       <c r="H13" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="58"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="L13" s="58"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1479,12 +1522,15 @@
       <c r="H14" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="38" t="s">
+      <c r="J14" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="K14" s="58"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="58"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="12">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1505,12 +1551,15 @@
       <c r="H15" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="K15" s="58"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="L15" s="58"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1523,12 +1572,13 @@
       <c r="F16" s="11"/>
       <c r="G16" s="36"/>
       <c r="H16" s="36"/>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="36"/>
+      <c r="K16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="58"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="58"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1549,12 +1599,15 @@
       <c r="H17" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="38" t="s">
+      <c r="J17" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="58"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="58"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1575,12 +1628,15 @@
       <c r="H18" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="K18" s="58"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="58"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1603,10 +1659,13 @@
       <c r="H19" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="J19" s="58"/>
+      <c r="J19" s="43" t="s">
+        <v>112</v>
+      </c>
       <c r="K19" s="58"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="58"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1629,10 +1688,13 @@
       <c r="H20" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="J20" s="58"/>
+      <c r="J20" s="61" t="s">
+        <v>134</v>
+      </c>
       <c r="K20" s="58"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="58"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1645,12 +1707,13 @@
       <c r="F21" s="11"/>
       <c r="G21" s="36"/>
       <c r="H21" s="36"/>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="36"/>
+      <c r="K21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="58"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="58"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1671,10 +1734,13 @@
       <c r="H22" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="J22" s="58"/>
+      <c r="J22" s="31" t="s">
+        <v>108</v>
+      </c>
       <c r="K22" s="58"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="58"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1695,10 +1761,13 @@
       <c r="H23" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="J23" s="58"/>
+      <c r="J23" s="31" t="s">
+        <v>136</v>
+      </c>
       <c r="K23" s="58"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="58"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="19">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1717,14 +1786,15 @@
         <v>106</v>
       </c>
       <c r="H24" s="35"/>
-      <c r="J24" s="58" t="s">
+      <c r="J24" s="67"/>
+      <c r="K24" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="60" t="s">
+      <c r="L24" s="60" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="19">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1743,14 +1813,15 @@
         <v>106</v>
       </c>
       <c r="H25" s="35"/>
-      <c r="J25" s="58" t="s">
+      <c r="J25" s="67"/>
+      <c r="K25" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="60" t="s">
+      <c r="L25" s="60" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1763,12 +1834,13 @@
       <c r="F26" s="11"/>
       <c r="G26" s="36"/>
       <c r="H26" s="36"/>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="67"/>
+      <c r="K26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K26" s="58"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="58"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="19">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1787,12 +1859,13 @@
         <v>106</v>
       </c>
       <c r="H27" s="35"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="60" t="s">
+      <c r="J27" s="67"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="60" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="19">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1813,10 +1886,11 @@
         <v>104</v>
       </c>
       <c r="H28" s="35"/>
-      <c r="J28" s="58"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="58"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="58"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="19">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1837,10 +1911,11 @@
         <v>104</v>
       </c>
       <c r="H29" s="35"/>
-      <c r="J29" s="58"/>
+      <c r="J29" s="67"/>
       <c r="K29" s="58"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="58"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="19">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1861,10 +1936,11 @@
         <v>104</v>
       </c>
       <c r="H30" s="35"/>
-      <c r="J30" s="58"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="58"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="58"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1877,12 +1953,13 @@
       <c r="F31" s="11"/>
       <c r="G31" s="36"/>
       <c r="H31" s="36"/>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="67"/>
+      <c r="K31" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K31" s="58"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="58"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="19">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1901,10 +1978,11 @@
         <v>104</v>
       </c>
       <c r="H32" s="35"/>
-      <c r="J32" s="58"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="58"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="58"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="19">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1919,10 +1997,11 @@
         <v>104</v>
       </c>
       <c r="H33" s="35"/>
-      <c r="J33" s="58"/>
+      <c r="J33" s="67"/>
       <c r="K33" s="58"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="58"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="62">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1943,12 +2022,15 @@
       <c r="H34" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="58"/>
-      <c r="K34" s="60" t="s">
+      <c r="J34" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="K34" s="58"/>
+      <c r="L34" s="60" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="62">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1969,12 +2051,15 @@
       <c r="H35" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="J35" s="20"/>
-      <c r="K35" s="60" t="s">
+      <c r="J35" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="K35" s="20"/>
+      <c r="L35" s="60" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="23">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1991,12 +2076,15 @@
       <c r="H36" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="24" t="s">
+      <c r="J36" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K36" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="K36" s="58"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L36" s="58"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="19">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2017,10 +2105,13 @@
       <c r="H37" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="J37" s="58"/>
+      <c r="J37" s="41" t="s">
+        <v>120</v>
+      </c>
       <c r="K37" s="58"/>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L37" s="58"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="19">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2033,30 +2124,34 @@
       <c r="F38" s="22"/>
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
-      <c r="J38" s="58"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="58"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B39" s="19">
+      <c r="L38" s="58"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" s="62">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="34" t="s">
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="J39" s="59" t="s">
+      <c r="H39" s="48"/>
+      <c r="J39" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="K39" s="58"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="58"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="19">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2071,10 +2166,11 @@
         <v>101</v>
       </c>
       <c r="H40" s="34"/>
-      <c r="J40" s="58"/>
+      <c r="J40" s="67"/>
       <c r="K40" s="58"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="58"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2087,12 +2183,13 @@
       <c r="F41" s="11"/>
       <c r="G41" s="36"/>
       <c r="H41" s="36"/>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="67"/>
+      <c r="K41" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K41" s="58"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="58"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="44">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2107,10 +2204,11 @@
         <v>36</v>
       </c>
       <c r="H42" s="48"/>
-      <c r="J42" s="58"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="58"/>
-    </row>
-    <row r="43" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L42" s="58"/>
+    </row>
+    <row r="43" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="49">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2125,8 +2223,11 @@
         <v>103</v>
       </c>
       <c r="H43" s="53"/>
-      <c r="J43" s="58"/>
+      <c r="J43" s="50" t="s">
+        <v>37</v>
+      </c>
       <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A808A401-4DEF-F24E-8B7E-1318F4C4FC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44D84A6-E32F-C64B-BB05-7D21C5F8D7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="132">
   <si>
     <t>Pin</t>
   </si>
@@ -374,12 +374,6 @@
     <t>DOWN Button</t>
   </si>
   <si>
-    <t>SYNC SW</t>
-  </si>
-  <si>
-    <t>SYNC Button</t>
-  </si>
-  <si>
     <t>JS8LED</t>
   </si>
   <si>
@@ -401,42 +395,6 @@
     <t>RXA</t>
   </si>
   <si>
-    <t>Digital RXA in</t>
-  </si>
-  <si>
-    <t>ADX-rp2040</t>
-  </si>
-  <si>
-    <t>Actions to take</t>
-  </si>
-  <si>
-    <t>TXLED</t>
-  </si>
-  <si>
-    <t>FT8LED</t>
-  </si>
-  <si>
-    <t>SW3 (TX)</t>
-  </si>
-  <si>
-    <t>SW1 (UP)</t>
-  </si>
-  <si>
-    <t>SW2 (DOWN)</t>
-  </si>
-  <si>
-    <t>+3.3V</t>
-  </si>
-  <si>
-    <t>Cut</t>
-  </si>
-  <si>
-    <t>Wire up</t>
-  </si>
-  <si>
-    <t>TXA</t>
-  </si>
-  <si>
     <t>Driver Enable</t>
   </si>
   <si>
@@ -446,28 +404,34 @@
     <t>RX Local Oscillator</t>
   </si>
   <si>
-    <t>RFIF</t>
-  </si>
-  <si>
-    <t>RF RX IF (465 KHz)</t>
-  </si>
-  <si>
-    <t>SDA(1)</t>
-  </si>
-  <si>
-    <t>SCL(1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C SDA </t>
-  </si>
-  <si>
-    <t>I2C SCL</t>
-  </si>
-  <si>
     <t>rp2040Z</t>
   </si>
   <si>
-    <t>Not used</t>
+    <t>RDX</t>
+  </si>
+  <si>
+    <t>RF(Q)</t>
+  </si>
+  <si>
+    <t>RST</t>
+  </si>
+  <si>
+    <t>RBPi Pico</t>
+  </si>
+  <si>
+    <t>Si4732 Reset (RST)</t>
+  </si>
+  <si>
+    <t>RFIF/RFQ</t>
+  </si>
+  <si>
+    <t>RFIF/RF(I)</t>
+  </si>
+  <si>
+    <t>RF RX IF ||  RF(I)</t>
+  </si>
+  <si>
+    <t>Receiver audio</t>
   </si>
 </sst>
 </file>
@@ -477,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,16 +464,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,7 +528,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -813,6 +775,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -876,14 +841,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -891,10 +848,41 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,13 +1175,13 @@
     <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="34.33203125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="8" max="10" width="13.1640625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,73 +1197,83 @@
       <c r="F3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="K3" s="57" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" s="57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="19">
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="20">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21" t="s">
+      <c r="D4" s="22"/>
+      <c r="E4" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="J4" s="66" t="s">
-        <v>143</v>
-      </c>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="19">
+      <c r="H4" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="36"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="67">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="35"/>
+      <c r="G5" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>48</v>
+      </c>
       <c r="J5" s="66" t="s">
-        <v>143</v>
-      </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="8">
         <f t="shared" ref="B6:B43" si="0">B5+1</f>
         <v>3</v>
@@ -1286,15 +1284,13 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" s="58"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="12">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1311,21 +1307,23 @@
       <c r="F7" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="58"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1342,21 +1340,23 @@
       <c r="F8" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="L8" s="58"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1373,21 +1373,23 @@
       <c r="F9" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="J9" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="L9" s="58"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="12">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1404,21 +1406,23 @@
       <c r="F10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="58"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1429,15 +1433,13 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L11" s="58"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="12">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1454,21 +1456,23 @@
       <c r="F12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="28" t="s">
+      <c r="G12" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="L12" s="58"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1485,26 +1489,28 @@
       <c r="F13" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="L13" s="58"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="37">
+      <c r="G13" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="38">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="14" t="s">
@@ -1516,26 +1522,28 @@
       <c r="F14" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="J14" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="L14" s="58"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="12">
+      <c r="G14" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="63">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="64" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="16"/>
@@ -1545,21 +1553,23 @@
       <c r="F15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="L15" s="58"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G15" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1570,20 +1580,18 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L16" s="58"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="37">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="38">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="39" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="6"/>
@@ -1593,26 +1601,28 @@
       <c r="F17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="G17" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="K17" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="L17" s="58"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" s="37">
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="39" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="6"/>
@@ -1622,50 +1632,56 @@
       <c r="F18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="43" t="s">
+      <c r="G18" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L18" s="58"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" s="37">
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G19" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1682,19 +1698,23 @@
       <c r="F20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="J20" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G20" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1705,15 +1725,13 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L21" s="58"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1728,19 +1746,23 @@
       <c r="F22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G22" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1755,73 +1777,77 @@
       <c r="F23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="J23" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="19">
+      <c r="G23" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="67">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32" t="s">
+      <c r="D24" s="33"/>
+      <c r="E24" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" s="35"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="58" t="s">
+      <c r="G24" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="L24" s="60" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="19">
+      <c r="H24" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="61"/>
+      <c r="J24" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="62"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="67">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32" t="s">
+      <c r="D25" s="33"/>
+      <c r="E25" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" s="35"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="58" t="s">
+      <c r="G25" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="L25" s="60" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H25" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="61"/>
+      <c r="J25" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="62"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1832,115 +1858,127 @@
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L26" s="58"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="19">
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B27" s="20">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21" t="s">
+      <c r="D27" s="22"/>
+      <c r="E27" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" s="35"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="60" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="19">
+      <c r="G27" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="61"/>
+      <c r="J27" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="62"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="20">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="35"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="19">
+      <c r="G28" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="61"/>
+      <c r="J28" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="62"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B29" s="20">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="35"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="19">
+      <c r="G29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="61"/>
+      <c r="J29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K29" s="62"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B30" s="20">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="35"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G30" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="61"/>
+      <c r="J30" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="62"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1951,224 +1989,232 @@
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L31" s="58"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="19">
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="20">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21" t="s">
+      <c r="D32" s="22"/>
+      <c r="E32" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="35"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
+      <c r="G32" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="61"/>
+      <c r="J32" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="62"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="19">
+      <c r="B33" s="20">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="35"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="61"/>
+      <c r="J33" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="62"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="62">
+      <c r="B34" s="76">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64" t="s">
+      <c r="D34" s="71"/>
+      <c r="E34" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="65" t="s">
+      <c r="F34" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="H34" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="J34" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="K34" s="58"/>
-      <c r="L34" s="60" t="s">
+      <c r="G34" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="73" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="K34" s="42" t="s">
         <v>131</v>
       </c>
+      <c r="L34" s="74"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="62">
+      <c r="B35" s="69">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64" t="s">
+      <c r="D35" s="71"/>
+      <c r="E35" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="65" t="s">
+      <c r="F35" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="H35" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="J35" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="K35" s="20"/>
-      <c r="L35" s="60" t="s">
-        <v>130</v>
-      </c>
+      <c r="G35" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="73" t="s">
+        <v>104</v>
+      </c>
+      <c r="L35" s="74"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="23">
+      <c r="B36" s="24">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="30" t="s">
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="30" t="s">
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="58"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="19">
+      <c r="B37" s="18">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21" t="s">
+      <c r="D37" s="22"/>
+      <c r="E37" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="H37" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="J37" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
+      <c r="G37" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="I37" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="J37" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="19">
+      <c r="B38" s="20">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="62">
+      <c r="B39" s="59">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="48" t="s">
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="H39" s="48"/>
-      <c r="J39" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="L39" s="58"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="19">
+      <c r="B40" s="20">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="34" t="s">
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
@@ -2181,57 +2227,53 @@
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L41" s="58"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="44">
+      <c r="B42" s="45">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C42" s="45" t="s">
+      <c r="C42" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="54" t="s">
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="48"/>
-      <c r="J42" s="67"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="58"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="49"/>
     </row>
     <row r="43" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+      <c r="B43" s="50">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="55" t="s">
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H43" s="53"/>
-      <c r="J43" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2245,7 +2287,7 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="57">
         <f>E2*6.25</f>
         <v>0</v>
       </c>
@@ -2255,7 +2297,7 @@
         <f>E2+1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="57">
         <f t="shared" ref="F3:F9" si="0">E3*6.25</f>
         <v>6.25</v>
       </c>
@@ -2265,7 +2307,7 @@
         <f t="shared" ref="E4:E9" si="1">E3+1</f>
         <v>2</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="57">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
@@ -2275,7 +2317,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="57">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
@@ -2285,7 +2327,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="57">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -2295,7 +2337,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="57">
         <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
@@ -2305,7 +2347,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="57">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
@@ -2315,12 +2357,13 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="57">
         <f t="shared" si="0"/>
         <v>43.75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44D84A6-E32F-C64B-BB05-7D21C5F8D7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC847C8-B590-CE47-A1A9-E7D7D36E301C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="131">
   <si>
     <t>Pin</t>
   </si>
@@ -417,9 +417,6 @@
   </si>
   <si>
     <t>RBPi Pico</t>
-  </si>
-  <si>
-    <t>Si4732 Reset (RST)</t>
   </si>
   <si>
     <t>RFIF/RFQ</t>
@@ -528,13 +525,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,21 +846,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -874,7 +870,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -883,6 +878,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1228,26 +1225,26 @@
       <c r="F4" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="65" t="s">
+      <c r="I4" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="76" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="36"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="67">
+      <c r="B5" s="66">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="67" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="22"/>
@@ -1257,21 +1254,19 @@
       <c r="F5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="66" t="s">
+      <c r="H5" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="65" t="s">
+      <c r="I5" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="66" t="s">
+      <c r="J5" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="65" t="s">
-        <v>127</v>
-      </c>
+      <c r="K5" s="36"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="8">
@@ -1539,11 +1534,11 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="63">
+      <c r="B15" s="62">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="63" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="16"/>
@@ -1553,17 +1548,17 @@
       <c r="F15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="65" t="s">
+      <c r="G15" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="J15" s="36" t="s">
-        <v>106</v>
+      <c r="J15" s="43" t="s">
+        <v>118</v>
       </c>
       <c r="K15" s="29" t="s">
         <v>119</v>
@@ -1747,19 +1742,19 @@
         <v>82</v>
       </c>
       <c r="G22" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="I22" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="32" t="s">
         <v>129</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
@@ -1794,11 +1789,11 @@
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="67">
+      <c r="B24" s="66">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="33"/>
@@ -1808,24 +1803,24 @@
       <c r="F24" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="65" t="s">
+      <c r="G24" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="61"/>
+      <c r="J24" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H24" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24" s="62"/>
+      <c r="K24" s="76"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="67">
+      <c r="B25" s="66">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="67" t="s">
         <v>22</v>
       </c>
       <c r="D25" s="33"/>
@@ -1835,17 +1830,17 @@
       <c r="F25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="65" t="s">
+      <c r="G25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="61"/>
+      <c r="J25" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="61"/>
-      <c r="J25" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="K25" s="62"/>
+      <c r="K25" s="76"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
@@ -1879,17 +1874,17 @@
       <c r="F27" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="36" t="s">
+      <c r="G27" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I27" s="61"/>
-      <c r="J27" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="62"/>
+      <c r="J27" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="76"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="20">
@@ -1908,17 +1903,17 @@
       <c r="F28" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="36" t="s">
+      <c r="G28" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I28" s="61"/>
-      <c r="J28" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K28" s="62"/>
+      <c r="J28" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="76"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="20">
@@ -1937,17 +1932,17 @@
       <c r="F29" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="36" t="s">
+      <c r="G29" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I29" s="61"/>
-      <c r="J29" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K29" s="62"/>
+      <c r="J29" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K29" s="76"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="20">
@@ -1966,17 +1961,17 @@
       <c r="F30" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="36" t="s">
+      <c r="G30" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I30" s="61"/>
-      <c r="J30" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K30" s="62"/>
+      <c r="J30" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="76"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
@@ -2010,17 +2005,17 @@
       <c r="F32" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="36" t="s">
+      <c r="G32" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I32" s="61"/>
-      <c r="J32" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K32" s="62"/>
+      <c r="J32" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="76"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="20">
@@ -2033,81 +2028,81 @@
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
       <c r="F33" s="23"/>
-      <c r="G33" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="36" t="s">
+      <c r="G33" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="76" t="s">
         <v>104</v>
       </c>
       <c r="I33" s="61"/>
-      <c r="J33" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="62"/>
+      <c r="J33" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="76"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="76">
+      <c r="B34" s="74">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71" t="s">
+      <c r="D34" s="70"/>
+      <c r="E34" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="72" t="s">
+      <c r="F34" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="73" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="75" t="s">
+      <c r="G34" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="73" t="s">
         <v>118</v>
       </c>
       <c r="K34" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="L34" s="74"/>
+        <v>130</v>
+      </c>
+      <c r="L34" s="72"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="69">
+      <c r="B35" s="68">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71" t="s">
+      <c r="D35" s="70"/>
+      <c r="E35" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K35" s="73" t="s">
-        <v>104</v>
-      </c>
-      <c r="L35" s="74"/>
+      <c r="G35" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="L35" s="72"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="24">
@@ -2154,11 +2149,11 @@
       <c r="I37" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="J37" s="36" t="s">
+      <c r="J37" s="76" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC847C8-B590-CE47-A1A9-E7D7D36E301C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B24FA4-860C-9A4F-9574-DCED952D382D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -846,40 +846,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1163,7 +1140,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L43"/>
+  <dimension ref="B2:K43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
@@ -1225,26 +1202,26 @@
       <c r="F4" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="66" t="s">
         <v>106</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="76" t="s">
+      <c r="J4" s="66" t="s">
         <v>104</v>
       </c>
       <c r="K4" s="36"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="66">
+      <c r="B5" s="62">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="63" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="22"/>
@@ -1789,11 +1766,11 @@
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="66">
+      <c r="B24" s="62">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="63" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="33"/>
@@ -1803,24 +1780,24 @@
       <c r="F24" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="76" t="s">
+      <c r="G24" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I24" s="61"/>
       <c r="J24" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="76"/>
+      <c r="K24" s="66"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="66">
+      <c r="B25" s="62">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="63" t="s">
         <v>22</v>
       </c>
       <c r="D25" s="33"/>
@@ -1830,17 +1807,17 @@
       <c r="F25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="76" t="s">
+      <c r="G25" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I25" s="61"/>
       <c r="J25" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="76"/>
+      <c r="K25" s="66"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
@@ -1874,17 +1851,17 @@
       <c r="F27" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="76" t="s">
+      <c r="G27" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I27" s="61"/>
-      <c r="J27" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="76"/>
+      <c r="J27" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="66"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="20">
@@ -1903,17 +1880,17 @@
       <c r="F28" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="76" t="s">
+      <c r="G28" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I28" s="61"/>
-      <c r="J28" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K28" s="76"/>
+      <c r="J28" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="66"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="20">
@@ -1932,17 +1909,17 @@
       <c r="F29" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="76" t="s">
+      <c r="G29" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I29" s="61"/>
-      <c r="J29" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K29" s="76"/>
+      <c r="J29" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K29" s="66"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="20">
@@ -1961,17 +1938,17 @@
       <c r="F30" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="76" t="s">
+      <c r="G30" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I30" s="61"/>
-      <c r="J30" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K30" s="76"/>
+      <c r="J30" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="66"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
@@ -2005,19 +1982,19 @@
       <c r="F32" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="76" t="s">
+      <c r="G32" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I32" s="61"/>
-      <c r="J32" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K32" s="76"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J32" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="66"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="20">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2028,83 +2005,81 @@
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
       <c r="F33" s="23"/>
-      <c r="G33" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="76" t="s">
+      <c r="G33" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="66" t="s">
         <v>104</v>
       </c>
       <c r="I33" s="61"/>
-      <c r="J33" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="76"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="74">
+      <c r="J33" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="66"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="18">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C34" s="75" t="s">
+      <c r="C34" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70" t="s">
+      <c r="D34" s="22"/>
+      <c r="E34" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="71" t="s">
+      <c r="F34" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="77" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="73" t="s">
+      <c r="G34" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="I34" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" s="42" t="s">
         <v>118</v>
       </c>
       <c r="K34" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="L34" s="72"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="68">
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="20">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70" t="s">
+      <c r="D35" s="22"/>
+      <c r="E35" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="71" t="s">
+      <c r="F35" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K35" s="77" t="s">
-        <v>104</v>
-      </c>
-      <c r="L35" s="72"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G35" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="66" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="24">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2125,12 +2100,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" s="18">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D37" s="22"/>
@@ -2140,23 +2115,23 @@
       <c r="F37" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="H37" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="I37" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="J37" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="K37" s="42" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G37" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="66" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" s="20">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2173,7 +2148,7 @@
       <c r="J38" s="36"/>
       <c r="K38" s="36"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" s="59">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2192,7 +2167,7 @@
       <c r="J39" s="49"/>
       <c r="K39" s="49"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B40" s="20">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2211,7 +2186,7 @@
       <c r="J40" s="35"/>
       <c r="K40" s="35"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2228,7 +2203,7 @@
       <c r="J41" s="37"/>
       <c r="K41" s="37"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B42" s="45">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2247,7 +2222,7 @@
       <c r="J42" s="55"/>
       <c r="K42" s="49"/>
     </row>
-    <row r="43" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="50">
         <f t="shared" si="0"/>
         <v>40</v>

--- a/doc/ADX-ddsPIO_pinout.xlsx
+++ b/doc/ADX-ddsPIO_pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/ADX-ddsPIO/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B24FA4-860C-9A4F-9574-DCED952D382D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A3C5F-C8DF-4A46-A757-66841E88DAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="760" windowWidth="26700" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="131">
   <si>
     <t>Pin</t>
   </si>
@@ -536,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -551,7 +551,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="dotted">
         <color indexed="64"/>
       </top>
       <bottom style="dotted">
@@ -566,7 +566,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="dotted">
         <color indexed="64"/>
       </top>
       <bottom style="dotted">
@@ -581,7 +581,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="dotted">
         <color indexed="64"/>
       </top>
       <bottom style="dotted">
@@ -599,7 +599,7 @@
       <top style="dotted">
         <color indexed="64"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -614,7 +614,7 @@
       <top style="dotted">
         <color indexed="64"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -629,67 +629,9 @@
       <top style="dotted">
         <color indexed="64"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -731,92 +673,128 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -825,38 +803,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,7 +1120,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K43"/>
+  <dimension ref="B3:K43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
@@ -1149,1097 +1129,1101 @@
     <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="34.33203125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="13.1640625" customWidth="1"/>
     <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="67" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="20">
+      <c r="B4" s="63">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" s="36"/>
+      <c r="J4" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="32"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="62">
+      <c r="B5" s="58">
         <f>B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="65" t="s">
+      <c r="H5" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="36"/>
+      <c r="K5" s="32"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <f t="shared" ref="B6:B43" si="0">B5+1</f>
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="12">
+      <c r="B7" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="25" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="12">
+      <c r="B8" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="25" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="12">
+      <c r="B9" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="12">
+      <c r="B10" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="25" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="8">
+      <c r="B11" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J12" s="43" t="s">
+      <c r="J12" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="25" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="43" t="s">
+      <c r="H13" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="J13" s="43" t="s">
+      <c r="J13" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="K13" s="43" t="s">
+      <c r="K13" s="39" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="38">
+      <c r="B14" s="34">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="J14" s="44" t="s">
+      <c r="J14" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K14" s="40" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="62">
+      <c r="B15" s="58">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
+      <c r="D15" s="13"/>
+      <c r="E15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="43" t="s">
+      <c r="G15" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="J15" s="43" t="s">
+      <c r="J15" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="8">
+      <c r="B16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="38">
+      <c r="B17" s="34">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="J17" s="44" t="s">
+      <c r="J17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="30" t="s">
+      <c r="K17" s="26" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="38">
+      <c r="B18" s="34">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="44" t="s">
+      <c r="J18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="26" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="4">
+      <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="H19" s="58" t="s">
+      <c r="H19" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="I19" s="58" t="s">
+      <c r="I19" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="J19" s="58" t="s">
+      <c r="J19" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="K19" s="32" t="s">
+      <c r="K19" s="28" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="4">
+      <c r="B20" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="J20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="K20" s="32" t="s">
+      <c r="K20" s="28" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="8">
+      <c r="B21" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="4">
+      <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="K22" s="32" t="s">
+      <c r="K22" s="28" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="4">
+      <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="J23" s="32" t="s">
+      <c r="J23" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K23" s="32" t="s">
+      <c r="K23" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="62">
+      <c r="B24" s="58">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33" t="s">
+      <c r="D24" s="29"/>
+      <c r="E24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="64" t="s">
+      <c r="G24" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="66"/>
+      <c r="H24" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="57"/>
+      <c r="J24" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="62"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="62">
+      <c r="B25" s="58">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33" t="s">
+      <c r="D25" s="29"/>
+      <c r="E25" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I25" s="61"/>
-      <c r="J25" s="64" t="s">
+      <c r="G25" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="66"/>
+      <c r="H25" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="57"/>
+      <c r="J25" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="62"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B26" s="8">
+      <c r="B26" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="20">
+      <c r="B27" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="61"/>
-      <c r="J27" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="66"/>
+      <c r="G27" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="57"/>
+      <c r="J27" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="62"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="20">
+      <c r="B28" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I28" s="61"/>
-      <c r="J28" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K28" s="66"/>
+      <c r="G28" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="57"/>
+      <c r="J28" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="62"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="20">
+      <c r="B29" s="17">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I29" s="61"/>
-      <c r="J29" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K29" s="66"/>
+      <c r="G29" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="57"/>
+      <c r="J29" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K29" s="62"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="20">
+      <c r="B30" s="17">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K30" s="66"/>
+      <c r="G30" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="57"/>
+      <c r="J30" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="62"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="8">
+      <c r="B31" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="20">
+      <c r="B32" s="17">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22" t="s">
+      <c r="D32" s="19"/>
+      <c r="E32" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="61"/>
-      <c r="J32" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K32" s="66"/>
+      <c r="G32" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="57"/>
+      <c r="J32" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="62"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="20">
+      <c r="B33" s="17">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I33" s="61"/>
-      <c r="J33" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="66"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="57"/>
+      <c r="J33" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="62"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="18">
+      <c r="B34" s="15">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="42" t="s">
+      <c r="G34" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="I34" s="42" t="s">
+      <c r="H34" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="J34" s="42" t="s">
+      <c r="I34" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="K34" s="42" t="s">
+      <c r="J34" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K34" s="38" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="20">
+      <c r="B35" s="17">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22" t="s">
+      <c r="D35" s="19"/>
+      <c r="E35" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K35" s="66" t="s">
+      <c r="G35" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="62" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="24">
+      <c r="B36" s="21">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="31" t="s">
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31" t="s">
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B37" s="18">
+      <c r="B37" s="15">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22" t="s">
+      <c r="D37" s="19"/>
+      <c r="E37" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="K37" s="66" t="s">
+      <c r="G37" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="62" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B38" s="20">
+      <c r="B38" s="17">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B39" s="59">
+      <c r="B39" s="55">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C39" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="49" t="s">
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="K39" s="45" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B40" s="20">
+      <c r="B40" s="17">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="35" t="s">
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B41" s="8">
+      <c r="B41" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B42" s="45">
+      <c r="B42" s="41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C42" s="46" t="s">
+      <c r="C42" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="55" t="s">
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="49"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="45"/>
     </row>
     <row r="43" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="50">
+      <c r="B43" s="46">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="56" t="s">
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="54"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2257,7 +2241,7 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F2" s="57">
+      <c r="F2" s="53">
         <f>E2*6.25</f>
         <v>0</v>
       </c>
@@ -2267,7 +2251,7 @@
         <f>E2+1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="53">
         <f t="shared" ref="F3:F9" si="0">E3*6.25</f>
         <v>6.25</v>
       </c>
@@ -2277,7 +2261,7 @@
         <f t="shared" ref="E4:E9" si="1">E3+1</f>
         <v>2</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="53">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
@@ -2287,7 +2271,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="53">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
@@ -2297,7 +2281,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -2307,7 +2291,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="53">
         <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
@@ -2317,7 +2301,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="53">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
@@ -2327,7 +2311,7 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="53">
         <f t="shared" si="0"/>
         <v>43.75</v>
       </c>
